--- a/astro-site/public/dl/plan-negocio-heladeria/checklist-apertura-heladeria.xlsx
+++ b/astro-site/public/dl/plan-negocio-heladeria/checklist-apertura-heladeria.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Alta censal (modelo 036/037) en los epígrafes 644.4 y 676 del IAE</t>
+          <t>Alta censal (modelo 036) en los epígrafes 644.4 y 676 del IAE</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>El 644.4 («comercio al por menor de helados») te permite fabricar helado y tartas heladas en el propio local para venderlos allí; el 676 cubre el consumo en mesas y terraza (RDLeg 1175/1990). Exento de cuota con una cifra de negocio inferior a 1 millón de euros</t>
+          <t>El 644.4 («comercio al por menor de helados») te permite fabricar helado y tartas heladas en el propio local para venderlos allí; el 676 cubre el consumo en mesas y terraza (RDLeg 1175/1990). Exento de cuota con una cifra de negocio inferior a 1 millón de euros (art. 82.1.c de la Ley de Haciendas Locales; confírmalo con tu gestoría)</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Declaración responsable de la actividad comercial (644.4)</t>
+          <t>Licencia, declaración o comunicación previa de la obra</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1206,12 +1206,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Antes de la obra</t>
+          <t>Semanas 6-8, antes de empezar la obra</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>La venta y fabricación de helado en el propio local, hasta 750 m², va por declaración responsable, sin licencia previa (Ley 12/2012, arts. 2-4 y anexo). Si la obra no necesita proyecto, tampoco necesita licencia (art. 3.3)</t>
+          <t>Pregunta en la consulta urbanística qué título pide tu obra. Sin proyecto, el art. 3.3 de la Ley 12/2012 la libera de licencia, pero no de la declaración responsable o la comunicación previa al ayuntamiento (art. 4)</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Licencia o declaración municipal de la parte de hostelería (676)</t>
+          <t>Declaración responsable de la actividad comercial (644.4)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Las mesas y el consumo en el local no están en el anexo de la Ley 12/2012: van por el régimen de tu ayuntamiento (licencia o declaración responsable, según la ordenanza)</t>
+          <t>La venta y fabricación de helado en el propio local, hasta 750 m², va por declaración responsable, sin licencia previa (Ley 12/2012, arts. 2-4 y anexo). La obra va por su propio trámite, en la tarea anterior</t>
         </is>
       </c>
     </row>
@@ -1250,22 +1250,22 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Solicitar la autorización de la terraza</t>
+          <t>Licencia o declaración municipal de la parte de hostelería (676)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Titular / Ayuntamiento</t>
+          <t>Técnico / Ayuntamiento</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Con la declaración responsable</t>
+          <t>Antes de la obra</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Es ocupación de la vía pública y siempre se pide aparte (Ley 12/2012, art. 2.2). Pregunta la tasa de tu ayuntamiento: la del plan es una cifra de ejemplo</t>
+          <t>Las mesas y el consumo en el local no están en el anexo de la Ley 12/2012: van por el régimen de tu ayuntamiento (licencia o declaración responsable, según la ordenanza)</t>
         </is>
       </c>
     </row>
@@ -1277,22 +1277,22 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Aumento de potencia a trifásica y boletín eléctrico</t>
+          <t>Solicitar la autorización de la terraza</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Instalador autorizado</t>
+          <t>Titular / Ayuntamiento</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Durante la obra</t>
+          <t>Con la declaración responsable</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Certificado de la instalación (boletín) para el nuevo contrato de luz</t>
+          <t>Es ocupación de la vía pública y siempre se pide aparte (Ley 12/2012, art. 2.2). Pregunta la tasa de tu ayuntamiento: la del plan es una cifra de ejemplo</t>
         </is>
       </c>
     </row>
@@ -1412,22 +1412,22 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Licencia o comunicación de la obra y certificado final</t>
+          <t>Aumento de potencia, boletín eléctrico y certificado final de obra</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Técnico</t>
+          <t>Instalador autorizado / Técnico</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Fin de la obra</t>
+          <t>Durante la obra y al acabarla</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Guarda el certificado final y el boletín: te los pedirá la declaración responsable de inicio</t>
+          <t>El boletín (certificado de la instalación) para el nuevo contrato de luz en trifásica y el certificado final del técnico. Guárdalos: te los pedirá la declaración responsable de inicio</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Antes de abrir</t>
+          <t>Antes de la primera tanda (también las de prueba)</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Vender helado a restaurantes o cafeterías de otra titularidad exige que sea marginal (el 25 % del volumen del año o 500 kg a la semana como máximo), de tu zona y a nadie inscrito en el RGSEAA, con una declaración responsable y el registro de destinatarios, cantidades y fechas</t>
+          <t>Vender helado a restaurantes o cafeterías de otra titularidad exige que sea marginal (lo que sirves a otros negocios, hasta el 25 % del volumen del año, o tu venta total, público incluido, hasta 500 kg a la semana), de tu zona y a nadie inscrito en el RGSEAA, con una declaración responsable y el registro de destinatarios, cantidades y fechas</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Orden de la mezcla: secos con el azúcar, líquidos, y grasas (nata, mantequilla), yemas y emulsionantes al subir, a 40-50 °C, ANTES de pasteurizar; después 85 °C, enfriado rápido a 4 °C o menos y maduración a 2-4 °C. Tras pasteurizar sólo entra lo que no necesita tratamiento (pastas puras, variegatos, fruta lavada de los sorbetes): nunca yema ni nata cruda</t>
+          <t>Orden de la mezcla: líquidos; secos premezclados con el azúcar, con el agitador en marcha; grasas (nata, mantequilla), yemas y emulsionantes al subir, a 40-50 °C, ANTES de pasteurizar; después 85 °C, enfriado rápido a 4 °C o menos y maduración a 2-4 °C. Tras pasteurizar sólo entra lo que no necesita tratamiento (pastas puras, variegatos, fruta lavada de los sorbetes): nunca yema ni nata cruda</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Clásicos, de temporada y uno o dos de autor; sorbetes sin lácteos para alérgicos y veganos</t>
+          <t>Clásicos, de temporada y uno o dos de autor; sorbetes sin lácteos en la receta para veganos y para quien no toma leche. A un cliente con alergia a la leche sírveselos sólo si los mantecas antes que los de leche, con la máquina recién limpia, y lo anotas en la ficha de alérgenos del sabor</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Octubre y enero</t>
+          <t>Septiembre y enero</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Fin de la temporada de cada fijo discontinuo por escrito y tres semanas de cierre en enero</t>
+          <t>Fin de la temporada de cada fijo discontinuo por escrito al acabar septiembre, y tres semanas de cierre en enero</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-heladeria/checklist-apertura-heladeria.xlsx
+++ b/astro-site/public/dl/plan-negocio-heladeria/checklist-apertura-heladeria.xlsx
@@ -951,8 +951,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1463,8 +1463,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1975,8 +1975,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2406,8 +2406,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2864,8 +2864,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -3322,8 +3322,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, —, N/A. N/A = no aplica, sale del total." type="list">
-      <formula1>"✓,—,N/A"</formula1>
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
+      <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
